--- a/artfynd/A 33321-2025 artfynd.xlsx
+++ b/artfynd/A 33321-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105165215</v>
+        <v>105165214</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1105</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608712.905032443</v>
+        <v>608723</v>
       </c>
       <c r="R2" t="n">
-        <v>7038677.86177629</v>
+        <v>7038718</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105165218</v>
+        <v>105165217</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608646.3452351462</v>
+        <v>608705</v>
       </c>
       <c r="R3" t="n">
-        <v>7038710.952587107</v>
+        <v>7038692</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,24 +844,14 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ett trettiotal</t>
+          <t>På gammal och grov samt dels med mossa överväxt tallåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105165214</v>
+        <v>105165209</v>
       </c>
       <c r="B4" t="n">
-        <v>90110</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1105</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608723.1883048053</v>
+        <v>608683</v>
       </c>
       <c r="R4" t="n">
-        <v>7038718.045619541</v>
+        <v>7038747</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -985,19 +950,14 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Någon enstaka</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,37 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105165216</v>
+        <v>105165218</v>
       </c>
       <c r="B5" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608707.4630274444</v>
+        <v>608647</v>
       </c>
       <c r="R5" t="n">
-        <v>7038692.893711726</v>
+        <v>7038711</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,19 +1056,14 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett trettiotal</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,37 +1094,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105165209</v>
+        <v>105165208</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608682.7447211654</v>
+        <v>608684</v>
       </c>
       <c r="R6" t="n">
-        <v>7038747.549596931</v>
+        <v>7038748</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,24 +1162,14 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Någon enstaka</t>
+          <t>Ett trettiotal</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,15 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105165208</v>
+        <v>105165216</v>
       </c>
       <c r="B7" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608684.0571952574</v>
+        <v>608708</v>
       </c>
       <c r="R7" t="n">
-        <v>7038748.489421309</v>
+        <v>7038693</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1338,24 +1268,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ett trettiotal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,37 +1301,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105165217</v>
+        <v>105165215</v>
       </c>
       <c r="B8" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608704.3599342223</v>
+        <v>608713</v>
       </c>
       <c r="R8" t="n">
-        <v>7038691.892860613</v>
+        <v>7038678</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1459,24 +1369,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gammal och grov samt dels med mossa överväxt tallåga</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 33321-2025 artfynd.xlsx
+++ b/artfynd/A 33321-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165214</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165217</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165209</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165218</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165208</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165216</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,8 +1434,22 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165215</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>